--- a/eval/results/evaluation_metrics_by_qid.xlsx
+++ b/eval/results/evaluation_metrics_by_qid.xlsx
@@ -1138,19 +1138,19 @@
         <v>120</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.875</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9574468085106383</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.7758620689655172</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1236,19 +1236,19 @@
         <v>120</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8083333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6379310344827587</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7628865979381444</v>
+        <v>0.75</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1257,7 +1257,7 @@
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -3294,19 +3294,19 @@
         <v>120</v>
       </c>
       <c r="B59" t="n">
-        <v>0.475</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4148936170212766</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.851063829787234</v>
       </c>
       <c r="E59" t="n">
-        <v>0.553191489361702</v>
+        <v>0.5633802816901409</v>
       </c>
       <c r="F59" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G59" t="n">
         <v>18</v>
@@ -3315,7 +3315,7 @@
         <v>55</v>
       </c>
       <c r="I59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3539,19 +3539,19 @@
         <v>120</v>
       </c>
       <c r="B64" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5916666666666667</v>
       </c>
       <c r="C64" t="n">
-        <v>0.48</v>
+        <v>0.4868421052631579</v>
       </c>
       <c r="D64" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5901639344262295</v>
+        <v>0.6016260162601627</v>
       </c>
       <c r="F64" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G64" t="n">
         <v>34</v>
@@ -3560,7 +3560,7 @@
         <v>39</v>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3637,19 +3637,19 @@
         <v>120</v>
       </c>
       <c r="B66" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="F66" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G66" t="n">
         <v>72</v>
@@ -3658,7 +3658,7 @@
         <v>8</v>
       </c>
       <c r="I66" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3735,19 +3735,19 @@
         <v>120</v>
       </c>
       <c r="B68" t="n">
-        <v>0.3833333333333334</v>
+        <v>0.4</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2976190476190476</v>
+        <v>0.313953488372093</v>
       </c>
       <c r="D68" t="n">
-        <v>0.625</v>
+        <v>0.675</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F68" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G68" t="n">
         <v>21</v>
@@ -3756,7 +3756,7 @@
         <v>59</v>
       </c>
       <c r="I68" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3882,19 +3882,19 @@
         <v>120</v>
       </c>
       <c r="B71" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C71" t="n">
-        <v>0.34</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="D71" t="n">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.3956043956043956</v>
       </c>
       <c r="F71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G71" t="n">
         <v>47</v>
@@ -3903,7 +3903,7 @@
         <v>33</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3980,19 +3980,19 @@
         <v>120</v>
       </c>
       <c r="B73" t="n">
-        <v>0.5583333333333333</v>
+        <v>0.575</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3673469387755102</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="D73" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4044943820224719</v>
+        <v>0.4395604395604396</v>
       </c>
       <c r="F73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G73" t="n">
         <v>49</v>
@@ -4001,7 +4001,7 @@
         <v>31</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -5891,19 +5891,19 @@
         <v>120</v>
       </c>
       <c r="B112" t="n">
-        <v>0.825</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9014084507042254</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="E112" t="n">
-        <v>0.8590604026845639</v>
+        <v>0.8513513513513514</v>
       </c>
       <c r="F112" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G112" t="n">
         <v>35</v>
@@ -5912,7 +5912,7 @@
         <v>14</v>
       </c>
       <c r="I112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5940,19 +5940,19 @@
         <v>120</v>
       </c>
       <c r="B113" t="n">
-        <v>0.775</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C113" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="D113" t="n">
-        <v>0.7183098591549296</v>
+        <v>0.704225352112676</v>
       </c>
       <c r="E113" t="n">
-        <v>0.7906976744186047</v>
+        <v>0.7812499999999999</v>
       </c>
       <c r="F113" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G113" t="n">
         <v>42</v>
@@ -5961,7 +5961,7 @@
         <v>7</v>
       </c>
       <c r="I113" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -6087,19 +6087,19 @@
         <v>120</v>
       </c>
       <c r="B116" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>0.5070422535211268</v>
+        <v>0.4929577464788732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6728971962616822</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="F116" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G116" t="n">
         <v>49</v>
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7410,19 +7410,19 @@
         <v>120</v>
       </c>
       <c r="B143" t="n">
-        <v>0.6083333333333333</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="C143" t="n">
-        <v>0.9622641509433962</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="D143" t="n">
-        <v>0.53125</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="E143" t="n">
-        <v>0.6845637583892618</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F143" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G143" t="n">
         <v>22</v>
@@ -7431,7 +7431,7 @@
         <v>2</v>
       </c>
       <c r="I143" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8275,19 +8275,19 @@
         <v>120</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.875</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9574468085106383</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.7758620689655172</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -8296,7 +8296,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -8373,19 +8373,19 @@
         <v>120</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8083333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6379310344827587</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7628865979381444</v>
+        <v>0.75</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -8394,7 +8394,7 @@
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -10431,19 +10431,19 @@
         <v>120</v>
       </c>
       <c r="B59" t="n">
-        <v>0.475</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4148936170212766</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.851063829787234</v>
       </c>
       <c r="E59" t="n">
-        <v>0.553191489361702</v>
+        <v>0.5633802816901409</v>
       </c>
       <c r="F59" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G59" t="n">
         <v>18</v>
@@ -10452,7 +10452,7 @@
         <v>55</v>
       </c>
       <c r="I59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -10676,19 +10676,19 @@
         <v>120</v>
       </c>
       <c r="B64" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5916666666666667</v>
       </c>
       <c r="C64" t="n">
-        <v>0.48</v>
+        <v>0.4868421052631579</v>
       </c>
       <c r="D64" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5901639344262295</v>
+        <v>0.6016260162601627</v>
       </c>
       <c r="F64" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G64" t="n">
         <v>34</v>
@@ -10697,7 +10697,7 @@
         <v>39</v>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -10774,19 +10774,19 @@
         <v>120</v>
       </c>
       <c r="B66" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="F66" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G66" t="n">
         <v>72</v>
@@ -10795,7 +10795,7 @@
         <v>8</v>
       </c>
       <c r="I66" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -10872,19 +10872,19 @@
         <v>120</v>
       </c>
       <c r="B68" t="n">
-        <v>0.3833333333333334</v>
+        <v>0.4</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2976190476190476</v>
+        <v>0.313953488372093</v>
       </c>
       <c r="D68" t="n">
-        <v>0.625</v>
+        <v>0.675</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="F68" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G68" t="n">
         <v>21</v>
@@ -10893,7 +10893,7 @@
         <v>59</v>
       </c>
       <c r="I68" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -11019,19 +11019,19 @@
         <v>120</v>
       </c>
       <c r="B71" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="C71" t="n">
-        <v>0.34</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="D71" t="n">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.3956043956043956</v>
       </c>
       <c r="F71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G71" t="n">
         <v>47</v>
@@ -11040,7 +11040,7 @@
         <v>33</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -11117,19 +11117,19 @@
         <v>120</v>
       </c>
       <c r="B73" t="n">
-        <v>0.5583333333333333</v>
+        <v>0.575</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3673469387755102</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="D73" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4044943820224719</v>
+        <v>0.4395604395604396</v>
       </c>
       <c r="F73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G73" t="n">
         <v>49</v>
@@ -11138,7 +11138,7 @@
         <v>31</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -13028,19 +13028,19 @@
         <v>120</v>
       </c>
       <c r="B112" t="n">
-        <v>0.825</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9014084507042254</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="E112" t="n">
-        <v>0.8590604026845639</v>
+        <v>0.8513513513513514</v>
       </c>
       <c r="F112" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G112" t="n">
         <v>35</v>
@@ -13049,7 +13049,7 @@
         <v>14</v>
       </c>
       <c r="I112" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -13077,19 +13077,19 @@
         <v>120</v>
       </c>
       <c r="B113" t="n">
-        <v>0.775</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C113" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="D113" t="n">
-        <v>0.7183098591549296</v>
+        <v>0.704225352112676</v>
       </c>
       <c r="E113" t="n">
-        <v>0.7906976744186047</v>
+        <v>0.7812499999999999</v>
       </c>
       <c r="F113" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G113" t="n">
         <v>42</v>
@@ -13098,7 +13098,7 @@
         <v>7</v>
       </c>
       <c r="I113" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -13224,19 +13224,19 @@
         <v>120</v>
       </c>
       <c r="B116" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>0.5070422535211268</v>
+        <v>0.4929577464788732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6728971962616822</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="F116" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G116" t="n">
         <v>49</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -14547,19 +14547,19 @@
         <v>120</v>
       </c>
       <c r="B143" t="n">
-        <v>0.6083333333333333</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="C143" t="n">
-        <v>0.9622641509433962</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="D143" t="n">
-        <v>0.53125</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="E143" t="n">
-        <v>0.6845637583892618</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F143" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G143" t="n">
         <v>22</v>
@@ -14568,7 +14568,7 @@
         <v>2</v>
       </c>
       <c r="I143" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>

--- a/eval/results/evaluation_metrics_by_qid.xlsx
+++ b/eval/results/evaluation_metrics_by_qid.xlsx
@@ -1040,19 +1040,19 @@
         <v>120</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8916666666666667</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9787234042553191</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.7758620689655172</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
         <v>61</v>
@@ -1061,7 +1061,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>120</v>
       </c>
       <c r="B15" t="n">
-        <v>0.875</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9574468085106383</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7758620689655172</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1236,19 +1236,19 @@
         <v>120</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8</v>
+        <v>0.8083333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.6379310344827587</v>
       </c>
       <c r="E17" t="n">
-        <v>0.75</v>
+        <v>0.7628865979381444</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1257,7 +1257,7 @@
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5842,19 +5842,19 @@
         <v>120</v>
       </c>
       <c r="B111" t="n">
-        <v>0.9083333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="C111" t="n">
-        <v>0.96875</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="D111" t="n">
-        <v>0.8732394366197183</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9185185185185184</v>
+        <v>0.9264705882352942</v>
       </c>
       <c r="F111" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G111" t="n">
         <v>47</v>
@@ -5863,7 +5863,7 @@
         <v>2</v>
       </c>
       <c r="I111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5891,19 +5891,19 @@
         <v>120</v>
       </c>
       <c r="B112" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.825</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="D112" t="n">
-        <v>0.8873239436619719</v>
+        <v>0.9014084507042254</v>
       </c>
       <c r="E112" t="n">
-        <v>0.8513513513513514</v>
+        <v>0.8590604026845639</v>
       </c>
       <c r="F112" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G112" t="n">
         <v>35</v>
@@ -5912,7 +5912,7 @@
         <v>14</v>
       </c>
       <c r="I112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5940,19 +5940,19 @@
         <v>120</v>
       </c>
       <c r="B113" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.775</v>
       </c>
       <c r="C113" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="D113" t="n">
-        <v>0.704225352112676</v>
+        <v>0.7183098591549296</v>
       </c>
       <c r="E113" t="n">
-        <v>0.7812499999999999</v>
+        <v>0.7906976744186047</v>
       </c>
       <c r="F113" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G113" t="n">
         <v>42</v>
@@ -5961,7 +5961,7 @@
         <v>7</v>
       </c>
       <c r="I113" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5989,19 +5989,19 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>0.85</v>
+        <v>0.8583333333333333</v>
       </c>
       <c r="C114" t="n">
-        <v>0.9818181818181818</v>
+        <v>0.9821428571428571</v>
       </c>
       <c r="D114" t="n">
-        <v>0.7605633802816901</v>
+        <v>0.7746478873239436</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8661417322834646</v>
       </c>
       <c r="F114" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G114" t="n">
         <v>48</v>
@@ -6010,7 +6010,7 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6038,19 +6038,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="n">
-        <v>0.8833333333333333</v>
+        <v>0.8916666666666667</v>
       </c>
       <c r="C115" t="n">
-        <v>0.9830508474576272</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="D115" t="n">
-        <v>0.8169014084507042</v>
+        <v>0.8309859154929577</v>
       </c>
       <c r="E115" t="n">
-        <v>0.8923076923076924</v>
+        <v>0.900763358778626</v>
       </c>
       <c r="F115" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G115" t="n">
         <v>48</v>
@@ -6059,7 +6059,7 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -8177,19 +8177,19 @@
         <v>120</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8916666666666667</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9787234042553191</v>
+        <v>0.9782608695652174</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.7758620689655172</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
         <v>61</v>
@@ -8198,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -8275,19 +8275,19 @@
         <v>120</v>
       </c>
       <c r="B15" t="n">
-        <v>0.875</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9574468085106383</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7758620689655172</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -8296,7 +8296,7 @@
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -8373,19 +8373,19 @@
         <v>120</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8</v>
+        <v>0.8083333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.6379310344827587</v>
       </c>
       <c r="E17" t="n">
-        <v>0.75</v>
+        <v>0.7628865979381444</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -8394,7 +8394,7 @@
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -12979,19 +12979,19 @@
         <v>120</v>
       </c>
       <c r="B111" t="n">
-        <v>0.9083333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="C111" t="n">
-        <v>0.96875</v>
+        <v>0.9692307692307692</v>
       </c>
       <c r="D111" t="n">
-        <v>0.8732394366197183</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9185185185185184</v>
+        <v>0.9264705882352942</v>
       </c>
       <c r="F111" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G111" t="n">
         <v>47</v>
@@ -13000,7 +13000,7 @@
         <v>2</v>
       </c>
       <c r="I111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -13028,19 +13028,19 @@
         <v>120</v>
       </c>
       <c r="B112" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.825</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="D112" t="n">
-        <v>0.8873239436619719</v>
+        <v>0.9014084507042254</v>
       </c>
       <c r="E112" t="n">
-        <v>0.8513513513513514</v>
+        <v>0.8590604026845639</v>
       </c>
       <c r="F112" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G112" t="n">
         <v>35</v>
@@ -13049,7 +13049,7 @@
         <v>14</v>
       </c>
       <c r="I112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -13077,19 +13077,19 @@
         <v>120</v>
       </c>
       <c r="B113" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.775</v>
       </c>
       <c r="C113" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.8793103448275862</v>
       </c>
       <c r="D113" t="n">
-        <v>0.704225352112676</v>
+        <v>0.7183098591549296</v>
       </c>
       <c r="E113" t="n">
-        <v>0.7812499999999999</v>
+        <v>0.7906976744186047</v>
       </c>
       <c r="F113" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G113" t="n">
         <v>42</v>
@@ -13098,7 +13098,7 @@
         <v>7</v>
       </c>
       <c r="I113" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -13126,19 +13126,19 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>0.85</v>
+        <v>0.8583333333333333</v>
       </c>
       <c r="C114" t="n">
-        <v>0.9818181818181818</v>
+        <v>0.9821428571428571</v>
       </c>
       <c r="D114" t="n">
-        <v>0.7605633802816901</v>
+        <v>0.7746478873239436</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8661417322834646</v>
       </c>
       <c r="F114" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G114" t="n">
         <v>48</v>
@@ -13147,7 +13147,7 @@
         <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -13175,19 +13175,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="n">
-        <v>0.8833333333333333</v>
+        <v>0.8916666666666667</v>
       </c>
       <c r="C115" t="n">
-        <v>0.9830508474576272</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="D115" t="n">
-        <v>0.8169014084507042</v>
+        <v>0.8309859154929577</v>
       </c>
       <c r="E115" t="n">
-        <v>0.8923076923076924</v>
+        <v>0.900763358778626</v>
       </c>
       <c r="F115" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G115" t="n">
         <v>48</v>
@@ -13196,7 +13196,7 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
